--- a/Mechanical/Connectors/Rectangular/Database/Mechanical_Connectors_Rectangular_1.25_GH_GOST.xlsx
+++ b/Mechanical/Connectors/Rectangular/Database/Mechanical_Connectors_Rectangular_1.25_GH_GOST.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,22 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Electronics\Mechanical\Connectors\Rectangular\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5107227-50D0-4246-ABC4-372F7190ECC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8379F688-311C-48DC-B7EC-C6EF8AF04C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11235"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -32,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="70">
   <si>
     <t>Item ID</t>
   </si>
@@ -236,12 +229,18 @@
   </si>
   <si>
     <t>Board_plug_6P</t>
+  </si>
+  <si>
+    <t>Shielding</t>
+  </si>
+  <si>
+    <t>Unshielded</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -566,8 +565,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
@@ -583,28 +582,28 @@
     <col min="12" max="14" width="7.140625" style="1" customWidth="1"/>
     <col min="15" max="15" width="13" style="1" customWidth="1"/>
     <col min="16" max="16" width="7.140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="7" style="1" customWidth="1"/>
-    <col min="19" max="19" width="4.5703125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="5.85546875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="4" style="1" customWidth="1"/>
-    <col min="22" max="23" width="6.140625" style="1" customWidth="1"/>
-    <col min="24" max="26" width="7.5703125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="6.28515625" style="1" customWidth="1"/>
-    <col min="28" max="28" width="5" style="1" customWidth="1"/>
-    <col min="29" max="31" width="7.85546875" style="1" customWidth="1"/>
-    <col min="32" max="32" width="13.140625" style="1" customWidth="1"/>
-    <col min="33" max="33" width="5.7109375" style="1" customWidth="1"/>
-    <col min="34" max="34" width="24.5703125" style="1" customWidth="1"/>
-    <col min="35" max="35" width="5.85546875" style="1" customWidth="1"/>
-    <col min="36" max="36" width="8.85546875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="18" width="6.7109375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7" style="1" customWidth="1"/>
+    <col min="20" max="20" width="4.5703125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="5.85546875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="4" style="1" customWidth="1"/>
+    <col min="23" max="24" width="6.140625" style="1" customWidth="1"/>
+    <col min="25" max="27" width="7.5703125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="6.28515625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="5" style="1" customWidth="1"/>
+    <col min="30" max="32" width="7.85546875" style="1" customWidth="1"/>
+    <col min="33" max="33" width="13.140625" style="1" customWidth="1"/>
+    <col min="34" max="34" width="5.7109375" style="1" customWidth="1"/>
+    <col min="35" max="35" width="24.5703125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="5.85546875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="8.85546875" style="1" customWidth="1"/>
+    <col min="38" max="38" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -657,73 +656,76 @@
         <v>36</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>62</v>
       </c>
@@ -773,45 +775,48 @@
         <v>44</v>
       </c>
       <c r="R2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AD2" s="2"/>
       <c r="AE2" s="2"/>
-      <c r="AF2" s="1" t="s">
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>56</v>
       </c>
@@ -861,41 +866,44 @@
         <v>44</v>
       </c>
       <c r="R3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AC3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="2"/>
       <c r="AE3" s="2"/>
-      <c r="AF3" s="1" t="s">
+      <c r="AF3" s="2"/>
+      <c r="AG3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AG3" s="1" t="s">
+      <c r="AH3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AH3" s="1" t="s">
+      <c r="AI3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AI3" s="1" t="s">
+      <c r="AJ3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AJ3" s="1" t="s">
+      <c r="AK3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AK3" s="1" t="s">
+      <c r="AL3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AL3" s="1" t="s">
+      <c r="AM3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AM3" s="1" t="s">
+      <c r="AN3" s="1" t="s">
         <v>49</v>
       </c>
     </row>

--- a/Mechanical/Connectors/Rectangular/Database/Mechanical_Connectors_Rectangular_1.25_GH_GOST.xlsx
+++ b/Mechanical/Connectors/Rectangular/Database/Mechanical_Connectors_Rectangular_1.25_GH_GOST.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Electronics\Mechanical\Connectors\Rectangular\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8379F688-311C-48DC-B7EC-C6EF8AF04C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A61C44A-8938-4CAA-98AA-05A24115EC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="99">
   <si>
     <t>Item ID</t>
   </si>
@@ -153,12 +154,6 @@
     <t>Row spacing</t>
   </si>
   <si>
-    <t>Vertical</t>
-  </si>
-  <si>
-    <t>Friction lock</t>
-  </si>
-  <si>
     <t>4 Wall</t>
   </si>
   <si>
@@ -177,64 +172,157 @@
     <t>Connector</t>
   </si>
   <si>
-    <t>Through hole</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
-    <t>2.54</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>PL</t>
-  </si>
-  <si>
-    <t>Pins Header</t>
-  </si>
-  <si>
-    <t>PLS-2.54-20P</t>
-  </si>
-  <si>
     <t>Black</t>
   </si>
   <si>
-    <t>Board_plug_20P</t>
-  </si>
-  <si>
     <t>..\Symbols\Mechanical_Connectors_Rectangular_GOST.SchLib</t>
   </si>
   <si>
-    <t>..\Footprints\Mechanical_Connectors_Rectangular_2.54_PL.PcbLib</t>
-  </si>
-  <si>
-    <t>Header</t>
-  </si>
-  <si>
-    <t>PLS-2.54-06P</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Connector header 2.54mm 06P vertical board</t>
-  </si>
-  <si>
-    <t>Connector header 2.54mm 20P vertical board</t>
-  </si>
-  <si>
-    <t>PLS-2.54-6P</t>
-  </si>
-  <si>
-    <t>Board_plug_6P</t>
-  </si>
-  <si>
     <t>Shielding</t>
   </si>
   <si>
     <t>Unshielded</t>
+  </si>
+  <si>
+    <t>GHR-10V-S</t>
+  </si>
+  <si>
+    <t>JST</t>
+  </si>
+  <si>
+    <t>SM10B-GHS-TB</t>
+  </si>
+  <si>
+    <t>1.25mm</t>
+  </si>
+  <si>
+    <t>Straight</t>
+  </si>
+  <si>
+    <t>GH</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Surface mount</t>
+  </si>
+  <si>
+    <t>Locking ramp</t>
+  </si>
+  <si>
+    <t>GH Connectors</t>
+  </si>
+  <si>
+    <t>Supplier 2</t>
+  </si>
+  <si>
+    <t>Supplier Part Number 2</t>
+  </si>
+  <si>
+    <t>ChipDip</t>
+  </si>
+  <si>
+    <t>9000380765</t>
+  </si>
+  <si>
+    <t>Board_socket_10P</t>
+  </si>
+  <si>
+    <t>Cable_plug_10P</t>
+  </si>
+  <si>
+    <t>8006798754</t>
+  </si>
+  <si>
+    <t>SSHL-002T-P0.2</t>
+  </si>
+  <si>
+    <t>Connector rectangular GH 1.25mm 10P right board</t>
+  </si>
+  <si>
+    <t>Connector rectangular GH 1.25mm 10P straight cable</t>
+  </si>
+  <si>
+    <t>Connector rectangular GH cable pin</t>
+  </si>
+  <si>
+    <t>Female pin</t>
+  </si>
+  <si>
+    <t>Pin</t>
+  </si>
+  <si>
+    <t>Wire</t>
+  </si>
+  <si>
+    <t>Cable mount</t>
+  </si>
+  <si>
+    <t>9000199678</t>
+  </si>
+  <si>
+    <t>Cable_pin</t>
+  </si>
+  <si>
+    <t>Unshroud</t>
+  </si>
+  <si>
+    <t>..\Footprints\Mechanical_Connectors_Rectangular_1.25_GH.PcbLib</t>
+  </si>
+  <si>
+    <t>Rectangular</t>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>50V</t>
+  </si>
+  <si>
+    <t>-40°C</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +105°C</t>
+  </si>
+  <si>
+    <t>13.75mm</t>
+  </si>
+  <si>
+    <t>0.80mm</t>
+  </si>
+  <si>
+    <t>4.80mm</t>
+  </si>
+  <si>
+    <t>1.00mm</t>
+  </si>
+  <si>
+    <t>15.75mm</t>
+  </si>
+  <si>
+    <t>4.25mm</t>
+  </si>
+  <si>
+    <t>5.13mm</t>
+  </si>
+  <si>
+    <t>4.15mm</t>
+  </si>
+  <si>
+    <t>5.70mm</t>
+  </si>
+  <si>
+    <t>https://www.jst-mfg.com/product/index.php?series=105&amp;lang=2</t>
+  </si>
+  <si>
+    <t>https://www.jst-mfg.com/product/pdf/eng/eGH.pdf</t>
   </si>
 </sst>
 </file>
@@ -566,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AP4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="1" customWidth="1"/>
@@ -580,7 +668,7 @@
     <col min="10" max="10" width="3.5703125" style="1" customWidth="1"/>
     <col min="11" max="11" width="3.28515625" style="1" customWidth="1"/>
     <col min="12" max="14" width="7.140625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" style="1" customWidth="1"/>
     <col min="16" max="16" width="7.140625" style="1" customWidth="1"/>
     <col min="17" max="18" width="6.7109375" style="1" customWidth="1"/>
     <col min="19" max="19" width="7" style="1" customWidth="1"/>
@@ -589,21 +677,24 @@
     <col min="22" max="22" width="4" style="1" customWidth="1"/>
     <col min="23" max="24" width="6.140625" style="1" customWidth="1"/>
     <col min="25" max="27" width="7.5703125" style="1" customWidth="1"/>
-    <col min="28" max="28" width="6.28515625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="5" style="1" customWidth="1"/>
-    <col min="30" max="32" width="7.85546875" style="1" customWidth="1"/>
-    <col min="33" max="33" width="13.140625" style="1" customWidth="1"/>
-    <col min="34" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="24.5703125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="5.85546875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="8.85546875" style="1" customWidth="1"/>
-    <col min="38" max="38" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="28" max="28" width="8.140625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="5.28515625" style="1" customWidth="1"/>
+    <col min="30" max="30" width="11.140625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="5" style="1" customWidth="1"/>
+    <col min="32" max="32" width="10.85546875" style="1" customWidth="1"/>
+    <col min="33" max="34" width="7.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="13.140625" style="1" customWidth="1"/>
+    <col min="36" max="36" width="5.7109375" style="1" customWidth="1"/>
+    <col min="37" max="37" width="24.5703125" style="1" customWidth="1"/>
+    <col min="38" max="38" width="5.85546875" style="1" customWidth="1"/>
+    <col min="39" max="39" width="8.85546875" style="1" customWidth="1"/>
+    <col min="40" max="40" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -656,7 +747,7 @@
         <v>36</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>35</v>
@@ -695,57 +786,66 @@
         <v>23</v>
       </c>
       <c r="AE1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>37</v>
@@ -754,162 +854,357 @@
         <v>38</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>46</v>
+      <c r="U2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="AC2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>59</v>
+      <c r="AE2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AJ2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>37</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>46</v>
+      <c r="U3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="AC3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AE3" s="2"/>
-      <c r="AF3" s="2"/>
-      <c r="AG3" s="1" t="s">
+      <c r="AE3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AH3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AJ3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AK3" s="1" t="s">
+      <c r="M4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AO4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP4" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="AL3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AM3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AN3" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="AH2" r:id="rId1" xr:uid="{1FB1054E-D74E-4AE9-B064-F9766D6DAAFA}"/>
+    <hyperlink ref="AH3" r:id="rId2" xr:uid="{6716134C-1338-4D50-9D77-87D759A18027}"/>
+    <hyperlink ref="AH4" r:id="rId3" xr:uid="{54CEC954-51C7-48FC-95D1-F073362AEE1F}"/>
+    <hyperlink ref="AG2" r:id="rId4" xr:uid="{8C0E90C0-CD12-4F7F-893A-6AC1244A97D3}"/>
+    <hyperlink ref="AG3" r:id="rId5" xr:uid="{DD489353-0145-42AC-8919-A462F26BF121}"/>
+    <hyperlink ref="AG4" r:id="rId6" xr:uid="{8708E727-ACBF-4AC1-8641-38D7E913DC69}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>